--- a/Spanish La Liga/Y.xlsx
+++ b/Spanish La Liga/Y.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3310"/>
+  <dimension ref="A1:C3319"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36844,6 +36844,105 @@
         <v>0.6774109579665982</v>
       </c>
     </row>
+    <row r="3311">
+      <c r="A3311" t="n">
+        <v>0.5106132458320504</v>
+      </c>
+      <c r="B3311" t="n">
+        <v>0.2768230301303317</v>
+      </c>
+      <c r="C3311" t="n">
+        <v>0.2125637240376179</v>
+      </c>
+    </row>
+    <row r="3312">
+      <c r="A3312" t="n">
+        <v>0.1806275722508228</v>
+      </c>
+      <c r="B3312" t="n">
+        <v>0.2288282240923836</v>
+      </c>
+      <c r="C3312" t="n">
+        <v>0.5905442036567936</v>
+      </c>
+    </row>
+    <row r="3313">
+      <c r="A3313" t="n">
+        <v>0.6010372343282916</v>
+      </c>
+      <c r="B3313" t="n">
+        <v>0.2482936589753205</v>
+      </c>
+      <c r="C3313" t="n">
+        <v>0.1506691066963877</v>
+      </c>
+    </row>
+    <row r="3314">
+      <c r="A3314" t="n">
+        <v>0.5225408119637275</v>
+      </c>
+      <c r="B3314" t="n">
+        <v>0.2557328829263715</v>
+      </c>
+      <c r="C3314" t="n">
+        <v>0.2217263051099011</v>
+      </c>
+    </row>
+    <row r="3315">
+      <c r="A3315" t="n">
+        <v>0.557840616966581</v>
+      </c>
+      <c r="B3315" t="n">
+        <v>0.2390745501285347</v>
+      </c>
+      <c r="C3315" t="n">
+        <v>0.2030848329048843</v>
+      </c>
+    </row>
+    <row r="3316">
+      <c r="A3316" t="n">
+        <v>0.2985677683360676</v>
+      </c>
+      <c r="B3316" t="n">
+        <v>0.2868592284013198</v>
+      </c>
+      <c r="C3316" t="n">
+        <v>0.4145730032626126</v>
+      </c>
+    </row>
+    <row r="3317">
+      <c r="A3317" t="n">
+        <v>0.3770087461919434</v>
+      </c>
+      <c r="B3317" t="n">
+        <v>0.298195153096614</v>
+      </c>
+      <c r="C3317" t="n">
+        <v>0.3247961007114426</v>
+      </c>
+    </row>
+    <row r="3318">
+      <c r="A3318" t="n">
+        <v>0.7800469021831631</v>
+      </c>
+      <c r="B3318" t="n">
+        <v>0.1356881585746302</v>
+      </c>
+      <c r="C3318" t="n">
+        <v>0.08426493924220667</v>
+      </c>
+    </row>
+    <row r="3319">
+      <c r="A3319" t="n">
+        <v>0.4381558932409531</v>
+      </c>
+      <c r="B3319" t="n">
+        <v>0.2913930564341383</v>
+      </c>
+      <c r="C3319" t="n">
+        <v>0.2704510503249086</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
